--- a/output/cs_report.xlsx
+++ b/output/cs_report.xlsx
@@ -482,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -494,7 +494,19 @@
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="4" customWidth="1" min="12" max="12"/>
+    <col width="4" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="4" customWidth="1" min="20" max="20"/>
+    <col width="18" customWidth="1" min="21" max="21"/>
+    <col width="18" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -535,7 +547,25 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Ср. оборот новых</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Общий оборот</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr"/>
+      <c r="M1" t="inlineStr"/>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Сегменты по обороту</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr"/>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Доходность</t>
         </is>
       </c>
     </row>
@@ -550,6 +580,52 @@
           <t>Активаций +%</t>
         </is>
       </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Starter
+&lt;$1k</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>Growth
+$1k-2k</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>Mid
+$2k-4k</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>Large
+$4k-8k</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>VIP
+$8k-16k</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise
+$16k+</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>Новых мерчей</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Общая за месяц</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -569,10 +645,10 @@
         <v>0</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3" s="7" t="n">
         <v>0</v>
@@ -581,7 +657,34 @@
         <v>0</v>
       </c>
       <c r="J3" s="7" t="n">
-        <v>80265.74000000001</v>
+        <v>0</v>
+      </c>
+      <c r="K3" s="7" t="n">
+        <v>51468</v>
+      </c>
+      <c r="N3" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="O3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" s="7" t="n">
+        <v>720.46</v>
       </c>
     </row>
     <row r="4">
@@ -596,25 +699,52 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>33.33</v>
+        <v>0</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G4" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="7" t="n">
+        <v>155559.66</v>
+      </c>
+      <c r="N4" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="O4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="H4" s="7" t="n">
-        <v>3432.77</v>
-      </c>
-      <c r="I4" s="7" t="n">
-        <v>118.37</v>
-      </c>
-      <c r="J4" s="7" t="n">
-        <v>170072.31</v>
+      <c r="Q4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="S4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="7" t="n">
+        <v>2694.16</v>
       </c>
     </row>
     <row r="5">
@@ -629,25 +759,52 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>4735.54</v>
+        <v>260.79</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>163.29</v>
+        <v>8.69</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>3226104.98</v>
+        <v>86.93000000000001</v>
+      </c>
+      <c r="K5" s="7" t="n">
+        <v>3330160.58</v>
+      </c>
+      <c r="N5" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="R5" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="S5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" s="7" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="V5" s="7" t="n">
+        <v>12604.9</v>
       </c>
     </row>
     <row r="6">
@@ -662,25 +819,52 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>1172.69</v>
+        <v>0</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>40.44</v>
+        <v>0</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>18997.32</v>
+        <v>0</v>
+      </c>
+      <c r="K6" s="7" t="n">
+        <v>24543.12</v>
+      </c>
+      <c r="N6" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="O6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="7" t="n">
+        <v>305.53</v>
       </c>
     </row>
     <row r="7">
@@ -695,25 +879,52 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N7" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="7" t="n">
-        <v>0</v>
+      <c r="O7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="7" t="n">
+        <v>0.04</v>
       </c>
     </row>
     <row r="8">
@@ -728,7 +939,7 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>0</v>
@@ -746,6 +957,33 @@
         <v>0</v>
       </c>
       <c r="J8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="O8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -781,6 +1019,33 @@
       <c r="J9" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="K9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -794,10 +1059,10 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>0</v>
@@ -806,47 +1071,107 @@
         <v>0</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>0</v>
+        <v>1916.6</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0</v>
+        <v>63.89</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>0</v>
+        <v>958.3</v>
+      </c>
+      <c r="K10" s="7" t="n">
+        <v>1916.6</v>
+      </c>
+      <c r="N10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="7" t="n">
+        <v>19.17</v>
+      </c>
+      <c r="V10" s="7" t="n">
+        <v>19.17</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" s="1" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>13.3325</v>
+        <v>9.375</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>19</v>
       </c>
       <c r="G11" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="H11" s="9" t="n">
+        <v>2177.39</v>
+      </c>
+      <c r="I11" s="9" t="n">
+        <v>9.0725</v>
+      </c>
+      <c r="J11" s="9" t="n">
+        <v>130.65375</v>
+      </c>
+      <c r="K11" s="9" t="n">
+        <v>3563652.46</v>
+      </c>
+      <c r="N11" s="1" t="n">
+        <v>62</v>
+      </c>
+      <c r="O11" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="P11" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="H11" s="9" t="n">
-        <v>9341</v>
-      </c>
-      <c r="I11" s="9" t="n">
-        <v>40.2625</v>
-      </c>
-      <c r="J11" s="9" t="n">
-        <v>3495440.35</v>
+      <c r="Q11" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="R11" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="S11" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="U11" s="9" t="n">
+        <v>21.78</v>
+      </c>
+      <c r="V11" s="9" t="n">
+        <v>16344.26</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="14">
     <mergeCell ref="I1:I2"/>
+    <mergeCell ref="M1:M2"/>
     <mergeCell ref="C1:D1"/>
+    <mergeCell ref="N1:S1"/>
+    <mergeCell ref="U1:V1"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="F1:F2"/>
+    <mergeCell ref="K1:K2"/>
     <mergeCell ref="H1:H2"/>
+    <mergeCell ref="L1:L2"/>
     <mergeCell ref="J1:J2"/>
+    <mergeCell ref="T1:T2"/>
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
